--- a/healthcare_forms/009_patient_extensive_intake_form--healthcare_forms.xlsx
+++ b/healthcare_forms/009_patient_extensive_intake_form--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1121,7 +1121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C91"/>
+  <dimension ref="A1:C88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="49" customWidth="1" min="1" max="1"/>
@@ -1982,17 +1982,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>medical_conditions_choices</t>
+          <t>medical_history_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>vitamin_b12_deficiency</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Vitamin B12 Deficiency</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2004,12 +2004,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>family_history</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Family History</t>
         </is>
       </c>
     </row>
@@ -2021,12 +2021,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>family_history</t>
+          <t>current_medical_history</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Family History</t>
+          <t>Current Medical History</t>
         </is>
       </c>
     </row>
@@ -2038,12 +2038,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>current_medical_history</t>
+          <t>past_medical_history</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Current Medical History</t>
+          <t>Past Medical History</t>
         </is>
       </c>
     </row>
@@ -2055,12 +2055,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>past_medical_history</t>
+          <t>surgical_history</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Past Medical History</t>
+          <t>Surgical History</t>
         </is>
       </c>
     </row>
@@ -2072,12 +2072,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>surgical_history</t>
+          <t>medication_history</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Surgical History</t>
+          <t>Medication History</t>
         </is>
       </c>
     </row>
@@ -2089,63 +2089,63 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>medication_history</t>
+          <t>social_history</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Medication History</t>
+          <t>Social History</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>medical_history_choices</t>
+          <t>patient_relationship_status_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>family_history</t>
+          <t>married</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Family History</t>
+          <t>Married</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>medical_history_choices</t>
+          <t>patient_relationship_status_choices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>social_history</t>
+          <t>single</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Social History</t>
+          <t>Single</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>medical_history_choices</t>
+          <t>patient_relationship_status_choices</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>surgical_history</t>
+          <t>divorced</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Surgical History</t>
+          <t>Divorced</t>
         </is>
       </c>
     </row>
@@ -2157,12 +2157,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>married</t>
+          <t>widowed</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Married</t>
+          <t>Widowed</t>
         </is>
       </c>
     </row>
@@ -2174,12 +2174,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>single</t>
+          <t>separated</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Separated</t>
         </is>
       </c>
     </row>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>divorced</t>
+          <t>in_a_relationship</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Divorced</t>
+          <t>In a Relationship</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>widowed</t>
+          <t>in_a_domestic_partnership</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Widowed</t>
+          <t>In a Domestic Partnership</t>
         </is>
       </c>
     </row>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>separated</t>
+          <t>in_a_civil_union</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Separated</t>
+          <t>In a Civil Union</t>
         </is>
       </c>
     </row>
@@ -2242,12 +2242,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>in_a_relationship</t>
+          <t>in_a_common_law_marriage</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>In a Relationship</t>
+          <t>In a Common Law Marriage</t>
         </is>
       </c>
     </row>
@@ -2259,12 +2259,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>in_a_domestic_partnership</t>
+          <t>in_a_same-sex_relationship</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>In a Domestic Partnership</t>
+          <t>In a Same-Sex Relationship</t>
         </is>
       </c>
     </row>
@@ -2276,63 +2276,63 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>in_a_civil_union</t>
+          <t>in_a_different_legal_jurisdiction</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>In a Civil Union</t>
+          <t>In a Different Legal Jurisdiction</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>patient_relationship_status_choices</t>
+          <t>emergency_contact_relationship_status_choices</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>in_a_common_law_marriage</t>
+          <t>mother</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>In a Common Law Marriage</t>
+          <t>Mother</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>patient_relationship_status_choices</t>
+          <t>emergency_contact_relationship_status_choices</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>in_a_same-sex_relationship</t>
+          <t>father</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>In a Same-Sex Relationship</t>
+          <t>Father</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>patient_relationship_status_choices</t>
+          <t>emergency_contact_relationship_status_choices</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>in_a_different_legal_jurisdiction</t>
+          <t>brother</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>In a Different Legal Jurisdiction</t>
+          <t>Brother</t>
         </is>
       </c>
     </row>
@@ -2344,12 +2344,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>mother</t>
+          <t>sister</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Sister</t>
         </is>
       </c>
     </row>
@@ -2361,12 +2361,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>father</t>
+          <t>spouse</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Spouse</t>
         </is>
       </c>
     </row>
@@ -2378,12 +2378,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>brother</t>
+          <t>partner</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Partner</t>
         </is>
       </c>
     </row>
@@ -2395,12 +2395,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>sister</t>
+          <t>friend</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Friend</t>
         </is>
       </c>
     </row>
@@ -2412,12 +2412,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>spouse</t>
+          <t>child</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spouse</t>
+          <t>Child</t>
         </is>
       </c>
     </row>
@@ -2429,12 +2429,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>partner</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Partner</t>
+          <t>Parent</t>
         </is>
       </c>
     </row>
@@ -2446,63 +2446,63 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>friend</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Friend</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>emergency_contact_relationship_status_choices</t>
+          <t>emergency_contact_relationship_status_2_choices</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>child</t>
+          <t>mother</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Child</t>
+          <t>Mother</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>emergency_contact_relationship_status_choices</t>
+          <t>emergency_contact_relationship_status_2_choices</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>parent</t>
+          <t>father</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Parent</t>
+          <t>Father</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>emergency_contact_relationship_status_choices</t>
+          <t>emergency_contact_relationship_status_2_choices</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>brother</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Brother</t>
         </is>
       </c>
     </row>
@@ -2514,12 +2514,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>mother</t>
+          <t>sister</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Sister</t>
         </is>
       </c>
     </row>
@@ -2531,12 +2531,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>father</t>
+          <t>spouse</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Spouse</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>brother</t>
+          <t>partner</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Partner</t>
         </is>
       </c>
     </row>
@@ -2565,12 +2565,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>sister</t>
+          <t>friend</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Friend</t>
         </is>
       </c>
     </row>
@@ -2582,12 +2582,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>spouse</t>
+          <t>child</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spouse</t>
+          <t>Child</t>
         </is>
       </c>
     </row>
@@ -2599,12 +2599,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>partner</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Partner</t>
+          <t>Parent</t>
         </is>
       </c>
     </row>
@@ -2616,61 +2616,10 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>friend</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
-        <is>
-          <t>Friend</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>emergency_contact_relationship_status_2_choices</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>child</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Child</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>emergency_contact_relationship_status_2_choices</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>parent</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Parent</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>emergency_contact_relationship_status_2_choices</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
